--- a/researchers_data.xlsx
+++ b/researchers_data.xlsx
@@ -458,7 +458,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['strategic management', 'business capabilities', 'organizational culture', 'leadership', 'competitive strategies', 'logistics strategies', 'supply chain management', 'logistics management']</t>
+          <t>['leadership', 'competitive strategies', 'logistics management', 'strategic management', 'supply chain management', 'organizational culture', 'logistics strategies', 'business capabilities']</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['cultural industries creative economy', 'art criticism philosophy art', 'cultural policy', 'cultural diplomacy']</t>
+          <t>['cultural diplomacy', 'art criticism philosophy art', 'cultural policy', 'cultural industries creative economy']</t>
         </is>
       </c>
     </row>
@@ -492,7 +492,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['biomechanics', 'centrifugal blood pump', 'biomedical instrumentation', 'pediatric ventricular assist device', 'biomedical sciences technologies']</t>
+          <t>['biomedical instrumentation', 'biomechanics', 'pediatric ventricular assist device', 'centrifugal blood pump', 'biomedical sciences technologies']</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['macroeconomics', 'monetary policy', 'growth', 'inflation']</t>
+          <t>['macroeconomics', 'inflation', 'growth', 'monetary policy']</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['restorative justice', 'justice theory', 'law society', 'criminology', 'penal policy', 'criminal justice', 'victimization harm', 'victimology', 'crime justice statistics', 'prisons', 'homicide femicide']</t>
+          <t>['criminology', 'criminal justice', 'victimology', 'restorative justice', 'homicide femicide', 'victimization harm', 'justice theory', 'crime justice statistics', 'law society', 'prisons', 'penal policy']</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['schizophrenia', 'mental health', 'immigration']</t>
+          <t>['schizophrenia', 'immigration', 'mental health']</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['green building certification systems', 'water efficiency', 'energy sustainability', 'passive system design', 'renewable energy', 'nzeb', '2030 sustainable development goals', 'hvac systems', 'waste heat energy', 'performance simulation', 'building energy performance']</t>
+          <t>['building energy performance', 'green building certification systems', 'renewable energy', 'nzeb', '2030 sustainable development goals', 'water efficiency', 'performance simulation', 'waste heat energy', 'passive system design', 'hvac systems', 'energy sustainability']</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['political life institutions türkiye', 'history turkish economy', 'history republic türkiye', ' history political parties türkiye']</t>
+          <t>['history republic türkiye', 'history turkish economy', 'political life institutions türkiye', ' history political parties türkiye']</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['ecological design', 'design with natural materials architecture', 'sustainable cities', 'soil architecture', 'biomaterials', 'performance based design', 'digital design production']</t>
+          <t>['soil architecture', 'ecological design', 'sustainable cities', 'digital design production', 'performance based design', 'design with natural materials architecture', 'biomaterials']</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['child wellbeing', 'disabled care)', 'elderly care', 'intersectional inequalities', 'welfare regimes', 'care policies (childcare', 'social policy', 'gender policies']</t>
+          <t>['disabled care)', 'care policies (childcare', 'gender policies', 'welfare regimes', 'elderly care', 'intersectional inequalities', 'child wellbeing', 'social policy']</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['optimization', 'biosensor development', 'dna binding proteins their tags', 'protein engineering']</t>
+          <t>['protein engineering', 'optimization', 'biosensor development', 'dna binding proteins their tags']</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['alkaliactivated binder systems', 'microstructure', 'durability', 'fiberreinforced cement based materials', 'rheological properties', 'sustainable construction materials', 'concrete technology']</t>
+          <t>['microstructure', 'fiberreinforced cement based materials', 'concrete technology', 'alkaliactivated binder systems', 'rheological properties', 'sustainable construction materials', 'durability']</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['modern city', 'creative analyzing', 'architectural design education', '20th century urban design history', 'urban morphology', 'collective spaces', 'modern architecture']</t>
+          <t>['modern architecture', 'creative analyzing', 'collective spaces', 'architectural design education', 'urban morphology', '20th century urban design history', 'modern city']</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['online retail', 'consumer ethics', 'experimental design', 'corporate social responsibility', 'consumer behavior']</t>
+          <t>['corporate social responsibility', 'consumer behavior', 'online retail', 'experimental design', 'consumer ethics']</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[' methodology', 'design studies', 'planning structures', 'theory', 'criticism', 'architectural', 'urban geography']</t>
+          <t>['architectural', 'theory', 'design studies', 'planning structures', ' methodology', 'urban geography', 'criticism']</t>
         </is>
       </c>
     </row>
@@ -747,7 +747,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['endodontics', 'pulp', 'cytotoxicity', 'biocompatibility', 'regeneration']</t>
+          <t>['pulp', 'regeneration', 'biocompatibility', 'endodontics', 'cytotoxicity']</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['architectural theory', 'architectural design', 'modern urban history', 'urbanizationarchitecture relationship', 'visual studies', 'architectural representation']</t>
+          <t>['architectural representation', 'urbanizationarchitecture relationship', 'architectural design', 'architectural theory', 'modern urban history', 'visual studies']</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['textile art', 'fiber art', 'textile history', 'weaving history', 'sustainable fashion practices']</t>
+          <t>['textile art', 'sustainable fashion practices', 'textile history', 'fiber art', 'weaving history']</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['international investment law', 'climate change', 'environmental law', 'alternative dispute resolution', 'world trade organization', 'competition law', 'international arbitration', 'international trade law', 'eu law', 'green consensus']</t>
+          <t>['environmental law', 'international trade law', 'international arbitration', 'eu law', 'climate change', 'international investment law', 'alternative dispute resolution', 'competition law', 'world trade organization', 'green consensus']</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['architectural design', 'new buildings historical environments', 'aesthetics place', 'interior design', 'theory restoration', 'traditional dwellings anatolia']</t>
+          <t>['traditional dwellings anatolia', 'architectural design', 'new buildings historical environments', 'theory restoration', 'interior design', 'aesthetics place']</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['entrepreneurship', 'consumer behavior', 'sustainable consumption']</t>
+          <t>['sustainable consumption', 'consumer behavior', 'entrepreneurship']</t>
         </is>
       </c>
     </row>
@@ -866,7 +866,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['business ethics', 'retailing', 'sustainability', 'social responsibility']</t>
+          <t>['business ethics', 'retailing', 'social responsibility', 'sustainability']</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['research performance', 'internationalization', 'higher education']</t>
+          <t>['higher education', 'research performance', 'internationalization']</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['behaviors financial consumers', 'consumer decision making systems', 'food waste attitudes behaviors consumers', 'physical activity motivation']</t>
+          <t>['food waste attitudes behaviors consumers', 'physical activity motivation', 'consumer decision making systems', 'behaviors financial consumers']</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>['architectural design', 'deep ecology', 'neoliberal urbanization processes', 'urban design', 'anthropocene']</t>
+          <t>['anthropocene', 'architectural design', 'deep ecology', 'urban design', 'neoliberal urbanization processes']</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>['tumor development', 'biochemistry', 'tumor biomarkers', 'biopolymer', 'enzymology', 'cancer biochemistry', 'food chemistry', 'lactose intolerance']</t>
+          <t>['biochemistry', 'cancer biochemistry', 'lactose intolerance', 'food chemistry', 'biopolymer', 'enzymology', 'tumor development', 'tumor biomarkers']</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['violence against women', 'migrant smuggling', 'victimoffender mediation', "victims' rights", 'criminal law', 'hate crimes', 'criminal procedure law', 'fundamental rights freedoms', 'banking crimes']</t>
+          <t>['migrant smuggling', 'fundamental rights freedoms', "victims' rights", 'violence against women', 'criminal procedure law', 'banking crimes', 'hate crimes', 'victimoffender mediation', 'criminal law']</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['medical history', 'gender', 'ottoman history', 'ottoman society']</t>
+          <t>['ottoman society', 'gender', 'ottoman history', 'medical history']</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['medical robotic systems', 'advanced motion control', 'teleoperation', 'control systems', 'prediction techniques', 'micromanipulation microrobotics']</t>
+          <t>['micromanipulation microrobotics', 'teleoperation', 'advanced motion control', 'control systems', 'medical robotic systems', 'prediction techniques']</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['multipurpose / hybrid offshore platforms', 'life cycle assessment (lca)', 'coastal structures', 'environmental sustainability', 'physical modeling', 'marine discharges', 'environmental impacts marine renewable energy systems']</t>
+          <t>['life cycle assessment (lca)', 'multipurpose / hybrid offshore platforms', 'environmental impacts marine renewable energy systems', 'marine discharges', 'coastal structures', 'physical modeling', 'environmental sustainability']</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['comparative law', 'law persons', 'low property law', 'contract law', 'eu data protection law', 'privacy', 'data protection', 'civil law', 'law obligations', 'civil liability']</t>
+          <t>['privacy', 'comparative law', 'eu data protection law', 'law persons', 'civil law', 'law obligations', 'civil liability', 'low property law', 'contract law', 'data protection']</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>['ultra wideband', 'high frequency technique', 'integrated circuits systems', 'sensor reader circuits', 'communication electronics']</t>
+          <t>['integrated circuits systems', 'sensor reader circuits', 'high frequency technique', 'ultra wideband', 'communication electronics']</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['mechanical failures', 'automotive aerospace materials', 'solid mechanics', 'fatigue engine parts', 'defense technologies', 'machine design', 'wear', 'internal combustion engines', 'computer aided machine design', 'lightweight vehicle design', 'computational mechanics']</t>
+          <t>['lightweight vehicle design', 'computational mechanics', 'internal combustion engines', 'fatigue engine parts', 'wear', 'defense technologies', 'computer aided machine design', 'mechanical failures', 'machine design', 'automotive aerospace materials', 'solid mechanics']</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['banking', 'small medium enterprises', 'time series analysis', 'green finance', 'qualitative finance', 'international finance', 'financial crises', 'risk management', 'quantitative', 'sustainable finance']</t>
+          <t>['sustainable finance', 'qualitative finance', 'financial crises', 'banking', 'green finance', 'time series analysis', 'risk management', 'small medium enterprises', 'quantitative', 'international finance']</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['applied macro', 'spatial econometrics', 'growth theory', 'international trade', 'economics', 'econometrics', 'macroeconomics']</t>
+          <t>['macroeconomics', 'econometrics', 'economics', 'spatial econometrics', 'applied macro', 'international trade', 'growth theory']</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['option pricing', 'mathematical finance', 'interest rate models', 'risk management']</t>
+          <t>['option pricing', 'risk management', 'interest rate models', 'mathematical finance']</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['media social change', 'press history', 'media literacy', 'digital media children', 'new media studies']</t>
+          <t>['new media studies', 'press history', 'media literacy', 'digital media children', 'media social change']</t>
         </is>
       </c>
     </row>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['theater', 'animation cinema', 'mythology', 'performance studies', 'cinema', 'performing arts', 'visual arts']</t>
+          <t>['performing arts', 'mythology', 'theater', 'animation cinema', 'cinema', 'visual arts', 'performance studies']</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>['rewriting', 'literature environment', 'theater', 'contemporary theories', 'mythology', 'adaptation']</t>
+          <t>['mythology', 'contemporary theories', 'adaptation', 'theater', 'rewriting', 'literature environment']</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['modern german history', 'dersim history', 'collective memory dating confrontation / reckoning', 'history ottoman railways', 'collective identities', 'ottoman constitutional history modern balkans abilities albanians (luke) history', 'cultural plurality language rights', 'modern ottoman republic türkiye socioeconomic', 'political intellectual history']</t>
+          <t>['ottoman constitutional history modern balkans abilities albanians (luke) history', 'cultural plurality language rights', 'political intellectual history', 'modern german history', 'modern ottoman republic türkiye socioeconomic', 'collective memory dating confrontation / reckoning', 'collective identities', 'dersim history', 'history ottoman railways']</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['social psychology', 'gender construction', 'health psychology', 'discrimination violence', 'gender', 'cultural context']</t>
+          <t>['gender', 'cultural context', 'gender construction', 'social psychology', 'health psychology', 'discrimination violence']</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['early ottoman archeology', 'urban history', 'islamic period tomb building inscriptions']</t>
+          <t>['islamic period tomb building inscriptions', 'early ottoman archeology', 'urban history']</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['social movements', 'civil society', 'political sociology', 'turkish political life', 'european studies', 'gender']</t>
+          <t>['social movements', 'turkish political life', 'gender', 'civil society', 'european studies', 'political sociology']</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['political science', 'political economy', 'political life institutions']</t>
+          <t>['political life institutions', 'political economy', 'political science']</t>
         </is>
       </c>
     </row>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['nursing', 'postoperative pain management', 'surgical nursing', 'cardiovascular nursing']</t>
+          <t>['postoperative pain management', 'cardiovascular nursing', 'surgical nursing', 'nursing']</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['motherhood attachment', 'psychotherapy processoutcome', 'emotion regulation', 'child psychopathology']</t>
+          <t>['psychotherapy processoutcome', 'child psychopathology', 'motherhood attachment', 'emotion regulation']</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['3d garment simulation', 'fashion supply chain', 'fit', 'virtual reality', 'comfort', 'fashion buying', 'artificial intelligence', 'fashion retail']</t>
+          <t>['comfort', 'fit', 'artificial intelligence', 'fashion supply chain', 'fashion buying', 'fashion retail', '3d garment simulation', 'virtual reality']</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['unification german principalities under prussian leadership emergence germany on historical stage', 'congress vienna napoleonic wars worker movements', '20th century thoughts revolutions antisemitism racism', 'late 19th century early 20th century political artistic economic sportive developments central europe', ' collapse empires building nation states', ' biedermeier age between 18151848 revolutionary aftermath']</t>
+          <t>['congress vienna napoleonic wars worker movements', 'unification german principalities under prussian leadership emergence germany on historical stage', ' collapse empires building nation states', 'late 19th century early 20th century political artistic economic sportive developments central europe', '20th century thoughts revolutions antisemitism racism', ' biedermeier age between 18151848 revolutionary aftermath']</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['international relations', 'foreign policy analysis dialectic', 'geopolitics']</t>
+          <t>['foreign policy analysis dialectic', 'international relations', 'geopolitics']</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['corporate marketing', 'consumer behavior', 'brand management', 'service marketing']</t>
+          <t>['corporate marketing', 'service marketing', 'consumer behavior', 'brand management']</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['anatomy', 'neuroanatomy', 'physiotherapy rehabilitation']</t>
+          <t>['physiotherapy rehabilitation', 'neuroanatomy', 'anatomy']</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['reliability validity', 'physiotherapy rehabilitation', 'ehealth', 'exercise', 'physiotherapy rehabilitation education informatics', 'telerehabilitation', 'quality life']</t>
+          <t>['exercise', 'quality life', 'ehealth', 'reliability validity', 'telerehabilitation', 'physiotherapy rehabilitation', 'physiotherapy rehabilitation education informatics']</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['generative ai', 'game development', 'ui ux design', 'media studies', 'medical technologies', 'architectural design computing', 'crossdomain tool development', 'xr technologies']</t>
+          <t>['crossdomain tool development', 'xr technologies', 'generative ai', 'architectural design computing', 'media studies', 'game development', 'medical technologies', 'ui ux design']</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['pregnancy', 'prenatalpostnatal period', 'holistic rehabilitation chronic diseases', 'healthy lifestyle exercises', 'incontinence', 'psychosocial rehabilitation', "women's health", 'rehabilitation', 'orthopedic rehabilitation', 'telerehabilitation', 'physiotherapy', 'infertility']</t>
+          <t>['orthopedic rehabilitation', "women's health", 'prenatalpostnatal period', 'rehabilitation', 'physiotherapy', 'infertility', 'psychosocial rehabilitation', 'healthy lifestyle exercises', 'pregnancy', 'telerehabilitation', 'holistic rehabilitation chronic diseases', 'incontinence']</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['ottoman islamic architecture history urbanism art', 'ottoman islamic landscape culture history', 'contemporary landscape design theory urbanism urban culture', 'architectural design']</t>
+          <t>['ottoman islamic architecture history urbanism art', 'architectural design', 'ottoman islamic landscape culture history', 'contemporary landscape design theory urbanism urban culture']</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['philosophy art', 'media archaeology', 'filmphilosophy', 'virtual reality', 'artificial intelligence']</t>
+          <t>['filmphilosophy', 'artificial intelligence', 'philosophy art', 'virtual reality', 'media archaeology']</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['human rights', 'freedoms', 'fundamental rights', 'philosophy law', 'history law']</t>
+          <t>['human rights', 'freedoms', 'philosophy law', 'fundamental rights', 'history law']</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['ethics law', 'legal philosophy', 'systems theory', 'law education', 'law literature', 'social theory law', 'legal methodology']</t>
+          <t>['law literature', 'law education', 'social theory law', 'legal philosophy', 'systems theory', 'legal methodology', 'ethics law']</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['relational psychoanalytic interpretations dreams symbols', 'defense mechanisms', 'relationship between affect therapeutic relationship psychotherapy outcome', 'adult psychotherapy process']</t>
+          <t>['defense mechanisms', 'relationship between affect therapeutic relationship psychotherapy outcome', 'adult psychotherapy process', 'relational psychoanalytic interpretations dreams symbols']</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>['society', 'identity', 'citizenship', 'school books']</t>
+          <t>['citizenship', 'school books', 'society', 'identity']</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['reproductive health', 'urogynecology', 'sexual health', "women's health", 'perinatal care', 'infertility']</t>
+          <t>['sexual health', 'perinatal care', "women's health", 'infertility', 'urogynecology', 'reproductive health']</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['partnership rights', 'dividend distribution limitations', 'transfer commercial enterprises', 'corporate law', 'commercial enterprise law']</t>
+          <t>['commercial enterprise law', 'corporate law', 'dividend distribution limitations', 'transfer commercial enterprises', 'partnership rights']</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['photography', 'animation', 'video', 'new media technologies', '2d - 3d computer graphics']</t>
+          <t>['animation', 'new media technologies', 'photography', '2d - 3d computer graphics', 'video']</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['kurdish cinema', 'short film', 'feminist film studies', 'film politics', 'documentary cinema', 'video essay', 'gender issues film industries']</t>
+          <t>['film politics', 'short film', 'feminist film studies', 'video essay', 'kurdish cinema', 'gender issues film industries', 'documentary cinema']</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['historiography', 'comparative historical sociology', 'early modern ottoman history', 'social economic history']</t>
+          <t>['comparative historical sociology', 'social economic history', 'early modern ottoman history', 'historiography']</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['media economy politics', 'screen studies', 'television culture', 'audience research']</t>
+          <t>['audience research', 'screen studies', 'media economy politics', 'television culture']</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['biomaterials', 'tissue engineering', 'controlled drug delivery systems', 'regenerative medicine']</t>
+          <t>['biomaterials', 'regenerative medicine', 'tissue engineering', 'controlled drug delivery systems']</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['language models', 'text/image processing', 'natural language processing', 'data science', 'machine learning', 'deep learning']</t>
+          <t>['text/image processing', 'language models', 'machine learning', 'natural language processing', 'deep learning', 'data science']</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['civil servants legislation', 'tax law', 'consumer law', 'environmental law', 'tax procedure law', 'administrative procedure law', 'health law', 'human rights law', 'zoning laws', 'administration law']</t>
+          <t>['tax law', 'health law', 'environmental law', 'human rights law', 'consumer law', 'tax procedure law', 'administrative procedure law', 'administration law', 'zoning laws', 'civil servants legislation']</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['intelligent reality', 'artificial intelligence', 'interactive 3d reconstruction']</t>
+          <t>['artificial intelligence', 'intelligent reality', 'interactive 3d reconstruction']</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['foreign language teaching', 'teaching turkish a foreign language', 'turkish language education', 'education']</t>
+          <t>['teaching turkish a foreign language', 'foreign language teaching', 'turkish language education', 'education']</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['validity', 'motor learning', 'reliability', "parkinson's disease", 'sustainability physiotherapy', 'environmental rehabilitation', 'posture disorders', 'rehabilitation technology', 'virtual reality based rehabilitation', 'physiotherapy', 'quality life', 'neural plasticity', 'joint protection principles', 'stroke', 'task oriented rehabilitation', 'spinal deformities', 'therapeutic exercise', 'rheumatological rehabilitation', 'delphi methodology', 'rehabilitation']</t>
+          <t>['quality life', 'environmental rehabilitation', 'stroke', 'rehabilitation technology', "parkinson's disease", 'motor learning', 'rehabilitation', 'sustainability physiotherapy', 'task oriented rehabilitation', 'reliability', 'posture disorders', 'therapeutic exercise', 'virtual reality based rehabilitation', 'joint protection principles', 'delphi methodology', 'neural plasticity', 'validity', 'spinal deformities', 'physiotherapy', 'rheumatological rehabilitation']</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['photography', 'animation', 'video', 'digital ethnography', 'visual analysis', '3d computer graphics', 'visual communication design']</t>
+          <t>['visual communication design', 'animation', 'photography', 'visual analysis', 'video', 'digital ethnography', '3d computer graphics']</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>['labor movement', 'political islam', 'electoral systems', 'coalition politics', 'radicalization', 'political elite', 'comparative politics', 'middle eastern elections political parties']</t>
+          <t>['middle eastern elections political parties', 'labor movement', 'radicalization', 'electoral systems', 'coalition politics', 'political elite', 'political islam', 'comparative politics']</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>['sustainability', 'management information system', 'decision support systems', 'supply chain management', 'logistics management']</t>
+          <t>['decision support systems', 'logistics management', 'supply chain management', 'management information system', 'sustainability']</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>['migrant workers', 'collective bargaining models', 'labor law', 'volunteering', 'new ways working', 'platform employees', 'teleworking', ' future work', 'social security law']</t>
+          <t>[' future work', 'new ways working', 'collective bargaining models', 'migrant workers', 'volunteering', 'labor law', 'teleworking', 'platform employees', 'social security law']</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['pediatrics', 'lymphedema', 'manuel therapy', 'orthopedics', 'rehabilitation', 'physiotherapy']</t>
+          <t>['orthopedics', 'rehabilitation', 'physiotherapy', 'manuel therapy', 'pediatrics', 'lymphedema']</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>['production planning', 'metaheuristic algorithms', 'operations research', 'logistics (warehouse management)', 'scheduling']</t>
+          <t>['logistics (warehouse management)', 'operations research', 'production planning', 'metaheuristic algorithms', 'scheduling']</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['modernism', 'meaning', 'airports', 'educational buildings', 'form', 'interior design', 'space']</t>
+          <t>['modernism', 'educational buildings', 'space', 'airports', 'interior design', 'meaning', 'form']</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['data mining', 'operations research', 'business intelligence', 'decision analysis']</t>
+          <t>['business intelligence', 'operations research', 'decision analysis', 'data mining']</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>['mindfulness', 'nursing image', 'critical thinking', 'organizational behavior', 'medical errors clinical risks management', 'nursing management', 'nursing education']</t>
+          <t>['critical thinking', 'organizational behavior', 'nursing management', 'medical errors clinical risks management', 'nursing image', 'mindfulness', 'nursing education']</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['functional upgrade', 'global value chains', 'design management', 'design ability']</t>
+          <t>['global value chains', 'design management', 'design ability', 'functional upgrade']</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>['biomedical mems biosensors', 'flexible disposable devices', 'microtechnology', 'biomedical imaging optics']</t>
+          <t>['microtechnology', 'biomedical imaging optics', 'biomedical mems biosensors', 'flexible disposable devices']</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['collective labor law', 'labor law', 'platform employees', 'social security law', 'teleworking']</t>
+          <t>['collective labor law', 'labor law', 'teleworking', 'platform employees', 'social security law']</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['human rights', 'social movements', 'sustainability', 'diversity inclusion', 'gender']</t>
+          <t>['social movements', 'human rights', 'diversity inclusion', 'gender', 'sustainability']</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>['arbitration', 'concordat', 'restructuring companies', 'civil procedure', 'civil procedure law', 'enforcement bankruptcy law', 'mediation']</t>
+          <t>['mediation', 'civil procedure law', 'concordat', 'arbitration', 'enforcement bankruptcy law', 'civil procedure', 'restructuring companies']</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>['iterated function systems', 'geometric measure theory', 'measure theory']</t>
+          <t>['geometric measure theory', 'measure theory', 'iterated function systems']</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['communication', 'twitter', 'contextual mapping', 'political economy data digital sociology', 'sociology', 'data visualization']</t>
+          <t>['contextual mapping', 'data visualization', 'political economy data digital sociology', 'communication', 'twitter', 'sociology']</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['brand management', 'reputation social responsibility', 'advertising', 'consumer behavior', 'marketing communication', 'research methods']</t>
+          <t>['advertising', 'research methods', 'consumer behavior', 'brand management', 'marketing communication', 'reputation social responsibility']</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['social movements', 'politics space', 'social theory', 'migration studies', 'sociology culture', 'historical sociology', 'urban studies']</t>
+          <t>['social movements', 'social theory', 'migration studies', 'historical sociology', 'politics space', 'sociology culture', 'urban studies']</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>['economic behavior', 'experimental economics', 'critical thinking']</t>
+          <t>['experimental economics', 'economic behavior', 'critical thinking']</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>['biomedical mems', 'biomedical electronics', 'magnetic mems', 'optical mems', 'mems microtechnology', 'electronic circuit design']</t>
+          <t>['biomedical mems', 'electronic circuit design', 'biomedical electronics', 'magnetic mems', 'optical mems', 'mems microtechnology']</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>['political movements history political thought', 'comparative political movements', 'political sociology']</t>
+          <t>['comparative political movements', 'political movements history political thought', 'political sociology']</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>['history design', 'design sustainability', 'design education', 'design thinking']</t>
+          <t>['design sustainability', 'design education', 'history design', 'design thinking']</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>['foreign investment law', 'international commercial arbitration', 'distribution agreements', 'international construction law', 'international private law', 'international family law', 'international commercial law']</t>
+          <t>['international commercial arbitration', 'international commercial law', 'international family law', 'foreign investment law', 'international construction law', 'international private law', 'distribution agreements']</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>['reputation management', 'corporate communication', 'crisis management', 'activist public relations', 'critical public relations', 'communication consultancy', 'crisis communication', 'public relations']</t>
+          <t>['communication consultancy', 'reputation management', 'crisis management', 'activist public relations', 'public relations', 'crisis communication', 'critical public relations', 'corporate communication']</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>['türkiyeeu relations', 'decolonization', 'french political history', 'european arts history', 'revolutionary changes world', 'european integration', 'colonialism', 'european political history']</t>
+          <t>['european integration', 'european arts history', 'colonialism', 'decolonization', 'türkiyeeu relations', 'french political history', 'european political history', 'revolutionary changes world']</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>['corporate communication', 'leadership', 'digital media', 'social inclusion', 'strategic communication']</t>
+          <t>['leadership', 'strategic communication', 'social inclusion', 'digital media', 'corporate communication']</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>['sustainable development goals', 'rights persons with disabilities', 'human rights older persons', 'humanitarian law']</t>
+          <t>['rights persons with disabilities', 'humanitarian law', 'sustainable development goals', 'human rights older persons']</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>['blockchain technology', 'gender', 'technology society', 'new communication technologies']</t>
+          <t>['new communication technologies', 'gender', 'technology society', 'blockchain technology']</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>['composition', 'performance', 'turkish music', 'improvisation', 'sound design', 'music theory']</t>
+          <t>['improvisation', 'performance', 'music theory', 'turkish music', 'composition', 'sound design']</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>['simulation optimization energy systems', 'energy electricity consumption estimation with data mining machine learning techniques', 'modeling', 'renewable energy types including solar wind bioenergy systems']</t>
+          <t>['renewable energy types including solar wind bioenergy systems', 'energy electricity consumption estimation with data mining machine learning techniques', 'simulation optimization energy systems', 'modeling']</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>['women entrepreneurs', 'leadership', 'women executive positions', 'stereotype threat', 'justice organizations', 'business models social enterprises']</t>
+          <t>['leadership', 'stereotype threat', 'women executive positions', 'business models social enterprises', 'women entrepreneurs', 'justice organizations']</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>['freight transportation', 'airport access', 'transportation planning', 'discrete choice models', 'mode choice', 'micromobility']</t>
+          <t>['transportation planning', 'airport access', 'micromobility', 'mode choice', 'freight transportation', 'discrete choice models']</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>['ottoman socioeconomic history', 'ottoman society', 'ottoman thought history', 'ottoman institutions civilization']</t>
+          <t>['ottoman society', 'ottoman thought history', 'ottoman institutions civilization', 'ottoman socioeconomic history']</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>['tool design', 'computation based design', 'digital craft', 'architectural geometry', 'digital design fabrication technologies', 'generative algorithms', 'robotic fabrication processes', 'material based design']</t>
+          <t>['digital craft', 'tool design', 'robotic fabrication processes', 'computation based design', 'architectural geometry', 'generative algorithms', 'digital design fabrication technologies', 'material based design']</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>['psychosocial challenges', 'professional quality life among healthcare professionals', 'psychosocial issues chronic illnesses']</t>
+          <t>['psychosocial challenges', 'psychosocial issues chronic illnesses', 'professional quality life among healthcare professionals']</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>['computer aided engineering', 'computational fluid mechanics', 'thermofluids']</t>
+          <t>['computer aided engineering', 'thermofluids', 'computational fluid mechanics']</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>['case method', 'innovation ecosystem', 'humantechnology interaction', 'entrepreneurship', 'sociomateriality', 'organizational routines', 'practice theory', 'institutional theory', 'power dynamics organizations', 'ethnography', 'discourse analysis', 'humanspace interaction', 'social movement dynamics']</t>
+          <t>['organizational routines', 'humanspace interaction', 'power dynamics organizations', 'practice theory', 'innovation ecosystem', 'social movement dynamics', 'case method', 'humantechnology interaction', 'sociomateriality', 'ethnography', 'discourse analysis', 'institutional theory', 'entrepreneurship']</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>['gesture', 'syntaxmorphology interface', 'syntaxphonology interface', 'prosody', 'language documentation']</t>
+          <t>['syntaxmorphology interface', 'syntaxphonology interface', 'prosody', 'language documentation', 'gesture']</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>['visual design applications', 'design thinking', 'transmedia journalism', 'transmedia storytelling', 'visual design theories']</t>
+          <t>['transmedia journalism', 'design thinking', 'transmedia storytelling', 'visual design theories', 'visual design applications']</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>['olympic games', 'physical activity', "women's sports", 'body sports sociology', 'migration', 'migrant athletes', 'women', 'fandom', 'gender']</t>
+          <t>['women', 'fandom', 'body sports sociology', 'physical activity', 'gender', 'migration', "women's sports", 'olympic games', 'migrant athletes']</t>
         </is>
       </c>
     </row>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>['system dynamics', 'urban analytics', 'spatiotemporal data analysis', 'spatiotemporal crime prediction', 'graph learning', 'data science', 'machine learning', 'deep learning']</t>
+          <t>['spatiotemporal data analysis', 'spatiotemporal crime prediction', 'deep learning', 'machine learning', 'urban analytics', 'graph learning', 'system dynamics', 'data science']</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>['directing', 'theater', 'actor training', 'michael chekhov acting technique', 'performing arts']</t>
+          <t>['performing arts', 'actor training', 'michael chekhov acting technique', 'directing', 'theater']</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>['therapeutic alliance', 'emotion regulation', 'mentalization', 'attachment', 'clinical psychology', 'psychodynamic psychotherapy']</t>
+          <t>['psychodynamic psychotherapy', 'clinical psychology', 'therapeutic alliance', 'attachment', 'mentalization', 'emotion regulation']</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>['critical media pedagogy', 'radio history', 'intercultural communication', 'feminist media', 'radio sound studies', 'participatory action research', 'gender media']</t>
+          <t>['participatory action research', 'feminist media', 'intercultural communication', 'radio sound studies', 'radio history', 'gender media', 'critical media pedagogy']</t>
         </is>
       </c>
     </row>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>['turkish economy political history', 'sociology work', 'organizational theory', 'political economy', 'situation theory', 'business history']</t>
+          <t>['situation theory', 'political economy', 'sociology work', 'business history', 'organizational theory', 'turkish economy political history']</t>
         </is>
       </c>
     </row>
@@ -2617,7 +2617,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>['urine protein analyses', 'tumor development', 'tumor biomarkers', 'cell biology', 'angiogenesis', 'composites', 'vascularization', 'protein biochemistry', 'proteomics', 'tissue engineering']</t>
+          <t>['protein biochemistry', 'urine protein analyses', 'composites', 'vascularization', 'tissue engineering', 'angiogenesis', 'proteomics', 'tumor development', 'cell biology', 'tumor biomarkers']</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>['law obligations', 'civil law']</t>
+          <t>['civil law', 'law obligations']</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>['braincomputer interface', 'machine learning artificial intelligence', 'electroencephalography', 'biomedical signal processing']</t>
+          <t>['machine learning artificial intelligence', 'biomedical signal processing', 'electroencephalography', 'braincomputer interface']</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>['data routing', ' heuristics', 'wireless sensor networks', 'activity scheduling']</t>
+          <t>['wireless sensor networks', 'activity scheduling', ' heuristics', 'data routing']</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>['sociology law', 'access justice studies', 'feminist legal theory', 'qualitative research methods', 'sociology professions', 'law society studies']</t>
+          <t>['law society studies', 'sociology law', 'sociology professions', 'qualitative research methods', 'access justice studies', 'feminist legal theory']</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>['mathematical modeling', 'nonlinear dynamics', 'safety', 'occupational accident', 'occupational health']</t>
+          <t>['occupational accident', 'safety', 'occupational health', 'nonlinear dynamics', 'mathematical modeling']</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>['architectural design theories', 'architectural filmmaking', 'spatial memory archive', 'architecture design education', 'critical spatial practices', 'architectural representation']</t>
+          <t>['architectural representation', 'architectural filmmaking', 'spatial memory archive', 'architectural design theories', 'architecture design education', 'critical spatial practices']</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>['educational technologies', 'vote', 'digital game']</t>
+          <t>['vote', 'digital game', 'educational technologies']</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>['architectural photogrammetry', 'adaptive reuse industrial heritage', 'history theory computational design', 'architectural restoration adaptive reuse', 'heritage tourism', 'serious games', 'new building design traditional fabric', 'conservation theories', 'traditional mediterranean architecture']</t>
+          <t>['architectural restoration adaptive reuse', 'history theory computational design', 'conservation theories', 'traditional mediterranean architecture', 'architectural photogrammetry', 'new building design traditional fabric', 'serious games', 'adaptive reuse industrial heritage', 'heritage tourism']</t>
         </is>
       </c>
     </row>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>['moral values', 'meaningful work', 'life satisfaction', 'values', 'value polarization', 'employee wellbeing']</t>
+          <t>['meaningful work', 'values', 'life satisfaction', 'moral values', 'value polarization', 'employee wellbeing']</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>['geotechnical laboratory field tests data acquisition systems', 'design with geosynthetics', 'polymer materials engineering behaviors civil engineering', 'poor soil characterization', 'geotechnical engineering', 'highways railways infrastructure design construction']</t>
+          <t>['geotechnical laboratory field tests data acquisition systems', 'polymer materials engineering behaviors civil engineering', 'poor soil characterization', 'highways railways infrastructure design construction', 'geotechnical engineering', 'design with geosynthetics']</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>['multiple sclerosis', 'cognitive rehabilitation', 'motor imagery', 'chronic pain', 'music therapy']</t>
+          <t>['multiple sclerosis', 'motor imagery', 'music therapy', 'chronic pain', 'cognitive rehabilitation']</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>['european convention human rights law', 'freedom religion belief', 'individual application constitutional court', 'freedom association', 'freedom expression', 'individual application european court human rights', 'nondiscrimination', 'constitutional law', 'freedom assembly', 'nongovernmental organizations', 'social rights', 'right education', 'freedom art', 'hate crimes', 'constitutional judiciary', 'hate speech', 'right be forgotten', 'human trafficking']</t>
+          <t>['individual application european court human rights', 'constitutional law', 'nondiscrimination', 'freedom assembly', 'individual application constitutional court', 'right education', 'freedom art', 'hate speech', 'right be forgotten', 'nongovernmental organizations', 'european convention human rights law', 'hate crimes', 'freedom religion belief', 'freedom expression', 'human trafficking', 'constitutional judiciary', 'freedom association', 'social rights']</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>['populism', 'political participation', 'citizenship', 'democracy', 'diasporas', 'nationalism', 'radicalism', 'migration', 'multiculturalism', 'migrant integration']</t>
+          <t>['multiculturalism', 'radicalism', 'political participation', 'migrant integration', 'diasporas', 'nationalism', 'democracy', 'citizenship', 'migration', 'populism']</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>['protection personal data', 'online child abuse', 'internet governance', 'biometric data', 'trust service provider', 'electronic seal', 'electronic commerce', 'digital service tax', 'server signing', 'online content moderation', 'information technology law', 'cyber security', 'privacy enhancing technologies', 'internet things', 'open data', 'time stamp', 'forensic informatics', 'digital transformation', 'cyber intelligence', 'open banking', 'blockchain', 'algorithmic transparency explainability', 'digital company', 'artificial intelligence', 'electronic payment services', 'digital services', 'industrial data', 'data governance', 'website authentication certificates', 'trust services', 'egovernment', 'electronic signature', 'registered electronic mail', 'cybercrime', 'privacy', 'electronic communications systems', 'commercial electronic communication']</t>
+          <t>['data governance', 'artificial intelligence', 'server signing', 'electronic payment services', 'trust services', 'cyber security', 'website authentication certificates', 'privacy enhancing technologies', 'information technology law', 'cyber intelligence', 'cybercrime', 'blockchain', 'egovernment', 'electronic signature', 'forensic informatics', 'online content moderation', 'digital transformation', 'algorithmic transparency explainability', 'internet governance', 'internet things', 'time stamp', 'commercial electronic communication', 'digital service tax', 'online child abuse', 'digital company', 'open data', 'registered electronic mail', 'digital services', 'privacy', 'electronic commerce', 'trust service provider', 'biometric data', 'protection personal data', 'electronic seal', 'electronic communications systems', 'industrial data', 'open banking']</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>['literature visuality', '20th century german literature', 'travel writing', 'exile literature', 'modern turkish literature', 'migration', 'literary modernism', 'brontë studies', 'literature film', 'evliya çelebi studies']</t>
+          <t>['brontë studies', 'literature visuality', '20th century german literature', 'travel writing', 'exile literature', 'evliya çelebi studies', 'migration', 'literature film', 'literary modernism', 'modern turkish literature']</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2923,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>['internal entrepreneurship', 'entrepreneurship', 'social entrepreneurship', 'change innovation', 'resilience', 'strategy', 'reputation']</t>
+          <t>['resilience', 'strategy', 'internal entrepreneurship', 'social entrepreneurship', 'change innovation', 'entrepreneurship', 'reputation']</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>['cultural landscapes', 'sustainable design', 'planning', 'tectonic culture', 'humanenvironment relationships', 'craft architecture', 'urban political ecology', 'architecture phenomenology']</t>
+          <t>['planning', 'sustainable design', 'humanenvironment relationships', 'urban political ecology', 'craft architecture', 'architecture phenomenology', 'cultural landscapes', 'tectonic culture']</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>['television studies', 'genre studies', 'television series', 'transnational adaptations']</t>
+          <t>['genre studies', 'television studies', 'transnational adaptations', 'television series']</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>['philosophy literature', 'ethics', 'contemporary french philosophy', 'philosophy social sciences', 'political philosophy']</t>
+          <t>['political philosophy', 'philosophy literature', 'contemporary french philosophy', 'ethics', 'philosophy social sciences']</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>['turkish', 'morphology', 'language acquisition', 'psycholinguistics', 'cognitive linguistics', 'linguistics']</t>
+          <t>['morphology', 'linguistics', 'psycholinguistics', 'language acquisition', 'cognitive linguistics', 'turkish']</t>
         </is>
       </c>
     </row>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>['artificial intelligence', 'science technology studies', 'assisted reproductive technologies', 'work', 'medical sociology', 'economic sociology', 'gender', 'automation', 'social policy']</t>
+          <t>['medical sociology', 'science technology studies', 'artificial intelligence', 'gender', 'economic sociology', 'work', 'automation', 'assisted reproductive technologies', 'social policy']</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>['political history türkiye', 'political theory', 'history political thinking', 'art', 'culture', 'feminism']</t>
+          <t>['history political thinking', 'art', 'political history türkiye', 'culture', 'political theory', 'feminism']</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>['social development', 'preschool education', 'early childhood development', 'classroom climate']</t>
+          <t>['social development', 'early childhood development', 'classroom climate', 'preschool education']</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>['occlusal splints', 'digital complete dentures', 'prosthodontic treatment', 'temporomandibular disorders', '3d printers', 'cad/cam technologies']</t>
+          <t>['occlusal splints', '3d printers', 'temporomandibular disorders', 'cad/cam technologies', 'digital complete dentures', 'prosthodontic treatment']</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>['democracy', 'news writing analysis', 'journalism', 'new media studies', 'media']</t>
+          <t>['new media studies', 'news writing analysis', 'democracy', 'media', 'journalism']</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>['comparative law', 'sale law', 'law obligations', 'trust law', 'property law']</t>
+          <t>['property law', 'comparative law', 'sale law', 'law obligations', 'trust law']</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>['technology fashion products', 'yarn', 'sustainable fashion', 'nanotechnology', 'knitting weaving technologies', 'technical textiles']</t>
+          <t>['technical textiles', 'nanotechnology', 'technology fashion products', 'knitting weaving technologies', 'sustainable fashion', 'yarn']</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>['virtual reality (vr)', 'machine learning (ml)', 'natural language processing (nlp)', 'augmented reality (ar)', 'metaverse', 'graphics programming', 'image processing', 'artificial intelligence (ai)']</t>
+          <t>['natural language processing (nlp)', 'image processing', 'virtual reality (vr)', 'metaverse', 'graphics programming', 'augmented reality (ar)', 'artificial intelligence (ai)', 'machine learning (ml)']</t>
         </is>
       </c>
     </row>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>['aesthetics architecture', 'theory', 'criticism', 'method architectural design', 'architecture', 'planning design']</t>
+          <t>['theory', 'architecture', 'planning design', 'method architectural design', 'aesthetics architecture', 'criticism']</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3212,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>['online marketing', 'advertising', 'consumer behavior', 'brand management']</t>
+          <t>['advertising', 'consumer behavior', 'online marketing', 'brand management']</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>['over urbanization', 'urban sprawl', 'right city']</t>
+          <t>['right city', 'over urbanization', 'urban sprawl']</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>['group psychotherapy', 'play', 'psychosocial intervention', 'creativity', 'positive clinical psychology', 'life satisfaction', 'bipolar disorders', 'wellbeing', 'early symptoms', 'art therapy', 'autism']</t>
+          <t>['autism', 'art therapy', 'play', 'wellbeing', 'psychosocial intervention', 'life satisfaction', 'positive clinical psychology', 'bipolar disorders', 'early symptoms', 'group psychotherapy', 'creativity']</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>['digitalization', 'deconstruction', 'communication philosophy', 'cultural theory', 'technology society']</t>
+          <t>['cultural theory', 'digitalization', 'communication philosophy', 'deconstruction', 'technology society']</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>['behavioral macroeconomics', 'experimental macroeconomics', 'dsge modelling', 'public policy preferences']</t>
+          <t>['dsge modelling', 'public policy preferences', 'experimental macroeconomics', 'behavioral macroeconomics']</t>
         </is>
       </c>
     </row>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>['language', 'sexuality gender football', 'ethics moral anthropology (via football', 'education urban space / traffic)']</t>
+          <t>['sexuality gender football', 'ethics moral anthropology (via football', 'language', 'education urban space / traffic)']</t>
         </is>
       </c>
     </row>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>['nonlinear analysis', 'structural dynamics', 'modal analysis', 'earthquake']</t>
+          <t>['nonlinear analysis', 'modal analysis', 'earthquake', 'structural dynamics']</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>['corporate governance', 'gender diversity', 'crowdfunding', 'sharing economy', 'alternative organizations']</t>
+          <t>['crowdfunding', 'alternative organizations', 'sharing economy', 'gender diversity', 'corporate governance']</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>['administrative law', 'administrative procedure law', 'public economic law']</t>
+          <t>['administrative procedure law', 'administrative law', 'public economic law']</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>['türkiyeeu relations', 'europeanisation', 'international organizations', 'european integration', 'social constructivism']</t>
+          <t>['europeanisation', 'european integration', 'international organizations', 'türkiyeeu relations', 'social constructivism']</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>['reverse logistics', 'multicriteria decision making', 'fuzzy sets its extensions', 'fuzzy multitarget mathematical programming', 'humanitarian logistics']</t>
+          <t>['multicriteria decision making', 'humanitarian logistics', 'reverse logistics', 'fuzzy multitarget mathematical programming', 'fuzzy sets its extensions']</t>
         </is>
       </c>
     </row>
@@ -3450,7 +3450,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>['software project management', 'enterprise software systems', 'software development processes', 'mobile multimedia communication', 'communication protocols', 'wireless sensor networks', 'database', 'data warehouse systems']</t>
+          <t>['software development processes', 'software project management', 'mobile multimedia communication', 'wireless sensor networks', 'database', 'enterprise software systems', 'data warehouse systems', 'communication protocols']</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>['sports economics', 'applied microeconomics']</t>
+          <t>['applied microeconomics', 'sports economics']</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>['jurisdiction over shipping', 'protection human rights sea', 'maritime security', 'public international law', 'irregular maritime migration', 'law sea', 'maritime delimitation']</t>
+          <t>['maritime security', 'protection human rights sea', 'irregular maritime migration', 'maritime delimitation', 'law sea', 'jurisdiction over shipping', 'public international law']</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>['dynamic', 'structural health monitoring wind earthquake response robotic systems', 'energy', 'mechanical', 'hydraulics']</t>
+          <t>['structural health monitoring wind earthquake response robotic systems', 'mechanical', 'hydraulics', 'dynamic', 'energy']</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>['foreign policy türkiye', "türkiye's eu membership pipelines", 'syria', 'russia', 'iran', 'relations with israel', ' pkk', "türkiye's military"]</t>
+          <t>['russia', 'relations with israel', ' pkk', "türkiye's eu membership pipelines", 'syria', 'iran', "türkiye's military", 'foreign policy türkiye']</t>
         </is>
       </c>
     </row>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>['selfdetermination theory', 'self identity workplace', 'leadership', 'organizational behavior', 'social sustainability', 'organizational psychology', 'sustainability organizations']</t>
+          <t>['leadership', 'organizational psychology', 'selfdetermination theory', 'sustainability organizations', 'social sustainability', 'organizational behavior', 'self identity workplace']</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>['cyber security', 'big data', 'blockchain', 'data mining', 'artificial intelligence']</t>
+          <t>['big data', 'artificial intelligence', 'blockchain', 'data mining', 'cyber security']</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>['special education', 'disability studies', 'inclusion', 'psychomotor development', 'early intervention']</t>
+          <t>['psychomotor development', 'special education', 'early intervention', 'disability studies', 'inclusion']</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>['ottoman period food beverage', 'enterprises', 'mevlevi culinary structure', 'sukiyabashi jiro &amp; el bulli &amp; le gavroche', 'haute cuisine vs avant garde cuisine', '15th century fatih period culinary culture']</t>
+          <t>['haute cuisine vs avant garde cuisine', 'mevlevi culinary structure', '15th century fatih period culinary culture', 'sukiyabashi jiro &amp; el bulli &amp; le gavroche', 'ottoman period food beverage', 'enterprises']</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>['video art / short film', 'video art', 'documentary', 'audiovisual production', 'contra']</t>
+          <t>['video art / short film', 'audiovisual production', 'contra', 'documentary', 'video art']</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3637,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>['storytelling', 'urban communication', 'experience design', 'information design', 'history design', 'visual culture', 'transmedia', 'design theories', 'visual storytelling', 'visual communication design', 'visual arts', 'urban graphics']</t>
+          <t>['visual communication design', 'history design', 'transmedia', 'storytelling', 'experience design', 'design theories', 'visual culture', 'visual storytelling', 'urban graphics', 'urban communication', 'information design', 'visual arts']</t>
         </is>
       </c>
     </row>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>['oral implantology', 'botulinum toxin (botox) injections', 'implant supported prostheses', 'dentistry', 'dental implant burs', 'oral maxillofacial surgery']</t>
+          <t>['botulinum toxin (botox) injections', 'dental implant burs', 'oral maxillofacial surgery', 'oral implantology', 'implant supported prostheses', 'dentistry']</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>['cryptocurrencies', 'carbon tax', 'sensitivity analysis', 'stochastic volatility', 'electricity prices volatility']</t>
+          <t>['electricity prices volatility', 'stochastic volatility', 'cryptocurrencies', 'sensitivity analysis', 'carbon tax']</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>['banking', 'environmental social governance (esg)', 'aidriven corporate performance', 'corporate governance', 'corporate finance', 'sustainable finance']</t>
+          <t>['sustainable finance', 'environmental social governance (esg)', 'aidriven corporate performance', 'corporate finance', 'banking', 'corporate governance']</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>['stabilization programs banking', 'financial forecasting modeling financial risk management']</t>
+          <t>['financial forecasting modeling financial risk management', 'stabilization programs banking']</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>['sports sciences', 'physical therapy rehabilitation']</t>
+          <t>['physical therapy rehabilitation', 'sports sciences']</t>
         </is>
       </c>
     </row>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>['hinfinity control', 'variable structure control', 'time delay systems', 'linear matrix inequalities', 'robust control']</t>
+          <t>['time delay systems', 'robust control', 'hinfinity control', 'variable structure control', 'linear matrix inequalities']</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>['computational methods', 'decolonial theories', 'home culture', 'digital fabrication', 'design anthropology', 'shape grammars', 'use design contexts']</t>
+          <t>['computational methods', 'decolonial theories', 'shape grammars', 'digital fabrication', 'design anthropology', 'home culture', 'use design contexts']</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>['economic security', 'political economy turkish foreign policy energy politics', 'balkans', 'eurasia', 'russia', 'international political economy']</t>
+          <t>['economic security', 'balkans', 'russia', 'international political economy', 'political economy turkish foreign policy energy politics', 'eurasia']</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>['media/digital anthropology', 'science technology studies (sts)', 'digital ethnography', 'digital disinformation', 'artificial intelligence ethics', 'literacy']</t>
+          <t>['literacy', 'artificial intelligence ethics', 'science technology studies (sts)', 'digital ethnography', 'media/digital anthropology', 'digital disinformation']</t>
         </is>
       </c>
     </row>
@@ -3841,7 +3841,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>['competition law policy', 'liability law', 'economic analysis law']</t>
+          <t>['competition law policy', 'economic analysis law', 'liability law']</t>
         </is>
       </c>
     </row>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>['vibration', 'finite element methods', 'energy density approach', 'residual stress analysis', 'cae methodology development', 'contact mechanics', 'welding', 'plasticity', 'simulation crash behavior', 'static dynamic fracture mechanics', 'user defined subroutines', 'parallel programming', 'computational mechanics', 'mechanical design optimization', 'mixedmode fatigue crack growth', 'structural analysis reliability', 'multiscale fracture', 'lowcycle highcycle fatigue', 'reliability analysis semiconductor packages']</t>
+          <t>['structural analysis reliability', 'computational mechanics', 'user defined subroutines', 'contact mechanics', 'mixedmode fatigue crack growth', 'lowcycle highcycle fatigue', 'static dynamic fracture mechanics', 'multiscale fracture', 'vibration', 'finite element methods', 'cae methodology development', 'reliability analysis semiconductor packages', 'energy density approach', 'residual stress analysis', 'plasticity', 'parallel programming', 'simulation crash behavior', 'welding', 'mechanical design optimization']</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>['microelectronics', 'biomedical', 'embedded system']</t>
+          <t>['biomedical', 'microelectronics', 'embedded system']</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>['molecular biology', 'gene polymorphism', 'genetic factors associated with antisocial behaviors aggression', 'immunology', 'monoaminoxidase a (maoa) gene', 'pathophysiology behavioral disorder gene polymorphisms related neurotransmitters']</t>
+          <t>['monoaminoxidase a (maoa) gene', 'immunology', 'pathophysiology behavioral disorder gene polymorphisms related neurotransmitters', 'molecular biology', 'genetic factors associated with antisocial behaviors aggression', 'gene polymorphism']</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>['impunity', 'freedom expression', 'criminology', 'penology', 'comparative criminal law', 'international criminal law', 'criminal justice', 'preventive police powers', 'child law juvenile courts', ' data protection law', 'human rights law', 'criminal law', 'hate crimes', 'criminal procedure law', 'hate speech']</t>
+          <t>['criminology', 'international criminal law', 'human rights law', 'comparative criminal law', ' data protection law', 'impunity', 'criminal justice', 'preventive police powers', 'child law juvenile courts', 'criminal procedure law', 'hate speech', 'penology', 'hate crimes', 'freedom expression', 'criminal law']</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>['nutritional supplements', 'medical nutrition therapy diseases', 'functional foods', 'clinical nutrition', 'sports nutrition', 'erogenic aids']</t>
+          <t>['nutritional supplements', 'medical nutrition therapy diseases', 'functional foods', 'sports nutrition', 'erogenic aids', 'clinical nutrition']</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>['gastrodiplomacy', 'turkish cuisine', 'local cuisines', 'gastronomy tourism', 'local agriculture']</t>
+          <t>['local agriculture', 'turkish cuisine', 'gastronomy tourism', 'local cuisines', 'gastrodiplomacy']</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>['decent work', 'organization theory', 'business history']</t>
+          <t>['organization theory', 'business history', 'decent work']</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>['impunity', 'human rights', 'restorative justice', 'violence against women', 'alternative dispute resolution - reconciliation', 'criminal criminal procedure law', 'sanction theory - confiscation', 'humanitarian law', 'hate crimes']</t>
+          <t>['human rights', 'sanction theory - confiscation', 'humanitarian law', 'impunity', 'violence against women', 'restorative justice', 'criminal criminal procedure law', 'alternative dispute resolution - reconciliation', 'hate crimes']</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>['sustainability', 'design education', 'design research methods', 'ergonomics', 'design management']</t>
+          <t>['design research methods', 'design education', 'ergonomics', 'design management', 'sustainability']</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>['artificial intelligence', 'machine learning', 'humanrobot interaction', 'digital image processing']</t>
+          <t>['digital image processing', 'artificial intelligence', 'humanrobot interaction', 'machine learning']</t>
         </is>
       </c>
     </row>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>['literature', 'environment literature', 'british american theater', 'theater film theories']</t>
+          <t>['environment literature', 'literature', 'british american theater', 'theater film theories']</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>['hurricanes', 'advanced data analysis', 'laboratory experiments', 'tides', 'rivers', 'hydrodynamics morphodynamics oceans', 'naturebased engineering solutions', 'turbulence', 'numerical modelling', 'nearshore coastal areas', 'currents', 'seas', 'sediment transport', 'lakes', 'field experiments', 'design water coastal structures', 'boundary layer', 'estuaries', 'waves']</t>
+          <t>['lakes', 'hydrodynamics morphodynamics oceans', 'sediment transport', 'naturebased engineering solutions', 'waves', 'turbulence', 'nearshore coastal areas', 'rivers', 'boundary layer', 'advanced data analysis', 'hurricanes', 'tides', 'laboratory experiments', 'currents', 'numerical modelling', 'estuaries', 'design water coastal structures', 'seas', 'field experiments']</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>['machine learning', 'computational social science', 'multimodal learning', 'natural language processing', 'network analysis']</t>
+          <t>['machine learning', 'computational social science', 'network analysis', 'natural language processing', 'multimodal learning']</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>['signal processing', 'machine learning', 'biomedical instrumentation']</t>
+          <t>['signal processing', 'biomedical instrumentation', 'machine learning']</t>
         </is>
       </c>
     </row>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>['2absorbent ideals commutative rings modules', 'finsler geometry', 'applications mathematical physics', 'riemannian geometry', 'commutative algebra', 'infinitesimal transformations some special riemann spaces', 'einstein finsler metrics']</t>
+          <t>['2absorbent ideals commutative rings modules', 'einstein finsler metrics', 'infinitesimal transformations some special riemann spaces', 'finsler geometry', 'applications mathematical physics', 'commutative algebra', 'riemannian geometry']</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>['socialecological studies', 'cultural studies', 'digital art', 'digital media', 'heritage', 'game design', 'critical play', 'visual culture', 'visual media communication design', 'critical media studies', 'contemporary art exhibitions', 'video game studies']</t>
+          <t>['digital art', 'cultural studies', 'heritage', 'critical play', 'visual media communication design', 'visual culture', 'game design', 'contemporary art exhibitions', 'digital media', 'video game studies', 'socialecological studies', 'critical media studies']</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>['social work', 'migration', 'children', 'seasonal agricultural work']</t>
+          <t>['seasonal agricultural work', 'migration', 'social work', 'children']</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>['self philosophies', 'ethics', 'philosophy literature']</t>
+          <t>['ethics', 'self philosophies', 'philosophy literature']</t>
         </is>
       </c>
     </row>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>['cultural studies', 'creative industry', 'creative labor', 'advertising history', 'advertising works']</t>
+          <t>['advertising history', 'cultural studies', 'creative industry', 'advertising works', 'creative labor']</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>['nonstate actors international law', 'international peace security law', 'human rights indicators', 'legal regime straits used international navigation montreux convention 1936', 'human rights activism (theoretical basis activism strategy)', 'space law', 'international law treaties', 'business human rights', 'international human rights law', 'monitoring review mechanisms international human rights law', 'international law']</t>
+          <t>['nonstate actors international law', 'monitoring review mechanisms international human rights law', 'international peace security law', 'human rights indicators', 'human rights activism (theoretical basis activism strategy)', 'international law treaties', 'space law', 'international human rights law', 'business human rights', 'international law', 'legal regime straits used international navigation montreux convention 1936']</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4215,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>['rna', 'dna', 'dna damage', 'cell viability', 'cell culture', 'toxicology', 'oxidative stress']</t>
+          <t>['oxidative stress', 'rna', 'dna damage', 'dna', 'toxicology', 'cell viability', 'cell culture']</t>
         </is>
       </c>
     </row>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>['literary biography', '18th century english literature', 'shakespeare', 'jane austen', 'history theory poetry', 'literary translation']</t>
+          <t>['literary biography', 'shakespeare', 'literary translation', 'history theory poetry', 'jane austen', '18th century english literature']</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>['danish cinema', 'documentary film', 'film social theory', 'feminist film theories']</t>
+          <t>['film social theory', 'documentary film', 'danish cinema', 'feminist film theories']</t>
         </is>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>['circular architecture', 'urban morphology', 'urban design', 'ecological urbanism', 'ecological restoration']</t>
+          <t>['circular architecture', 'urban morphology', 'ecological urbanism', 'urban design', 'ecological restoration']</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4283,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>['physics', 'mathematical physics', 'dynamical systems', 'nonlinear dynamical systems', 'chaotic systems', 'statistical physics', 'high energy particle physics', 'condensed matter physics']</t>
+          <t>['physics', 'nonlinear dynamical systems', 'chaotic systems', 'mathematical physics', 'condensed matter physics', 'dynamical systems', 'high energy particle physics', 'statistical physics']</t>
         </is>
       </c>
     </row>
@@ -4300,7 +4300,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>['world politics', 'international relations', 'distance education', 'hybrid', 'digitization', 'turkish foreign policy']</t>
+          <t>['world politics', 'hybrid', 'turkish foreign policy', 'distance education', 'international relations', 'digitization']</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>['communication research', 'communication theories', 'social media', 'gender', 'new media']</t>
+          <t>['gender', 'social media', 'new media', 'communication theories', 'communication research']</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>['cultural studies', 'ethnographic fieldwork', 'music sociology', 'musicology', 'contemporary music scene türkiye']</t>
+          <t>['cultural studies', 'contemporary music scene türkiye', 'music sociology', 'ethnographic fieldwork', 'musicology']</t>
         </is>
       </c>
     </row>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>['social movements', 'political sociology', 'social theory', 'intellectual history', 'historical sociology', 'turkish politics', 'giftgiving', 'social memory']</t>
+          <t>['social memory', 'social movements', 'giftgiving', 'social theory', 'historical sociology', 'intellectual history', 'political sociology', 'turkish politics']</t>
         </is>
       </c>
     </row>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>['financial biases', 'risk preference', 'financial literacy', 'experimental economics', 'intergenerational transmission', 'behavioral economics', 'behavioral finance']</t>
+          <t>['behavioral finance', 'financial literacy', 'risk preference', 'intergenerational transmission', 'behavioral economics', 'experimental economics', 'financial biases']</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4402,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>['human resources management', 'strategic business management', 'aviation management', 'leadership motivation', 'management organization']</t>
+          <t>['aviation management', 'human resources management', 'strategic business management', 'management organization', 'leadership motivation']</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>['organizational psychology', 'crosscultural management', 'organizational behavior']</t>
+          <t>['organizational behavior', 'crosscultural management', 'organizational psychology']</t>
         </is>
       </c>
     </row>
@@ -4453,7 +4453,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>['model theory', 'group theory']</t>
+          <t>['group theory', 'model theory']</t>
         </is>
       </c>
     </row>
@@ -4470,7 +4470,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>['local food', 'gastronomy tourism', 'food heritage', 'functional foods']</t>
+          <t>['gastronomy tourism', 'local food', 'food heritage', 'functional foods']</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>['computer aided drug design', 'molecular modeling', 'statistical modeling', 'functional genomics', 'biomolecular interactions']</t>
+          <t>['molecular modeling', 'functional genomics', 'statistical modeling', 'biomolecular interactions', 'computer aided drug design']</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>['molecular imaging', 'radiation physics', 'single photon emission tomography', 'positron emission tomography', 'medical data analytics', 'nuclear medicine', 'radionuclide dosimetry', 'medical imaging']</t>
+          <t>['nuclear medicine', 'positron emission tomography', 'single photon emission tomography', 'radionuclide dosimetry', 'medical data analytics', 'radiation physics', 'medical imaging', 'molecular imaging']</t>
         </is>
       </c>
     </row>
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>['conceptual design', 'evaluation', 'design education', 'graphic representation']</t>
+          <t>['conceptual design', 'design education', 'evaluation', 'graphic representation']</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>['musicology', 'music', 'music theory', 'musical composition']</t>
+          <t>['musical composition', 'musicology', 'music', 'music theory']</t>
         </is>
       </c>
     </row>
@@ -4555,7 +4555,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>['information technology', 'spreadsheet', 'word processing', 'database', 'presentation']</t>
+          <t>['presentation', 'word processing', 'spreadsheet', 'database', 'information technology']</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>['political sociology', 'political movements history political thought', 'political science methodology']</t>
+          <t>['political science methodology', 'political movements history political thought', 'political sociology']</t>
         </is>
       </c>
     </row>
@@ -4589,7 +4589,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>['climate change', 'ecological citizenship', 'sustainable transport', 'circular economy', 'smart cities', 'energy water policies', 'carbon pricing']</t>
+          <t>['energy water policies', 'ecological citizenship', 'circular economy', 'sustainable transport', 'carbon pricing', 'climate change', 'smart cities']</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>['theory interiority interior (urban interiors', 'history criticism (bodyspace relationship', 'spirituality', 'architectural interior design (design methodologies', 'architectural theory', 'embodiment', 'computational thought', 'spatial narratives', 'utopias', 'cemetery death studies)', 'visual narratives', 'temporality', 'ecology)', 'spatial experience', 'historical experience', 'design education)']</t>
+          <t>['cemetery death studies)', 'ecology)', 'spatial narratives', 'architectural theory', 'history criticism (bodyspace relationship', 'historical experience', 'architectural interior design (design methodologies', 'spatial experience', 'temporality', 'utopias', 'computational thought', 'design education)', 'embodiment', 'spirituality', 'theory interiority interior (urban interiors', 'visual narratives']</t>
         </is>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>['spectroscopic analysis methods', 'aroma active phenolic compounds', 'enzyme technology', 'sensor development', 'food chemistry', 'biotechnological processes']</t>
+          <t>['enzyme technology', 'food chemistry', 'sensor development', 'aroma active phenolic compounds', 'biotechnological processes', 'spectroscopic analysis methods']</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>['ancient greek roman art architecture', 'history architecture', 'cultural heritage reuse', 'presentation archaeological sites museums', 'basic design']</t>
+          <t>['history architecture', 'basic design', 'presentation archaeological sites museums', 'cultural heritage reuse', 'ancient greek roman art architecture']</t>
         </is>
       </c>
     </row>
@@ -4657,7 +4657,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>['forensic accounting', 'financial reporting', 'accounting education', 'financial analysis']</t>
+          <t>['financial analysis', 'financial reporting', 'accounting education', 'forensic accounting']</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>['graphic design', 'artificial intelligence', 'ui/ux', 'movie design', 'game design', 'architectural digital design', 'animation', 'augmented reality', '3d design', 'virtual reality', 'motion graphic design', 'visual effect', '3d typography']</t>
+          <t>['3d design', 'visual effect', 'augmented reality', 'artificial intelligence', 'animation', 'ui/ux', 'motion graphic design', 'game design', '3d typography', 'graphic design', 'movie design', 'architectural digital design', 'virtual reality']</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>['gender equality', 'empowerment', 'physical activity', 'sports', 'sociology sports', 'serious leisure physical activity', 'gender', "women's empowerment", 'media']</t>
+          <t>['sociology sports', 'gender equality', "women's empowerment", 'physical activity', 'gender', 'media', 'serious leisure physical activity', 'sports', 'empowerment']</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>['violence against women', 'qualitative research methods', 'dating violence', 'prevention intervention studies mental health', 'gender psychology', 'feminist psychology']</t>
+          <t>['prevention intervention studies mental health', 'feminist psychology', 'violence against women', 'qualitative research methods', 'gender psychology', 'dating violence']</t>
         </is>
       </c>
     </row>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>['intergenerational relationships', 'grandparenting', 'aging', 'autonomy development', 'parenting']</t>
+          <t>['intergenerational relationships', 'aging', 'grandparenting', 'parenting', 'autonomy development']</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>['integration highend design production technologies design education', 'philosophy technology architecture', 'ontology', 'sustainable futures', 'selforganizing structures life fictions', 'first year design education', 'architectural design architectural theory', 'nonhierarchical']</t>
+          <t>['integration highend design production technologies design education', 'first year design education', 'architectural design architectural theory', 'selforganizing structures life fictions', 'sustainable futures', 'ontology', 'philosophy technology architecture', 'nonhierarchical']</t>
         </is>
       </c>
     </row>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>['commercial law', 'capital markets law', 'company law']</t>
+          <t>['capital markets law', 'commercial law', 'company law']</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>['international arbitration', 'alternative dispute resolution (adr)', 'private international law']</t>
+          <t>['private international law', 'alternative dispute resolution (adr)', 'international arbitration']</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>['architectural geometry', 'robotics', 'computational design', 'digital fabrication technologies', 'coding']</t>
+          <t>['digital fabrication technologies', 'computational design', 'architectural geometry', 'coding', 'robotics']</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>['convergence hypothesis', 'convergans clubs', 'maximum clique algorithm', 'growth economy']</t>
+          <t>['growth economy', 'convergence hypothesis', 'maximum clique algorithm', 'convergans clubs']</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>['youth work', 'universitycivil society relations', 'public economy', 'civil society capacity strengthening', 'child studies']</t>
+          <t>['youth work', 'universitycivil society relations', 'civil society capacity strengthening', 'child studies', 'public economy']</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>['artificial intelligence', 'machine learning', 'natural language processing', 'deep learning']</t>
+          <t>['artificial intelligence', 'natural language processing', 'machine learning', 'deep learning']</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>['machine learning', 'metaheuristic approaches', 'transportation logistics problems', 'operations research']</t>
+          <t>['transportation logistics problems', 'metaheuristic approaches', 'operations research', 'machine learning']</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>['ferroelectric materials', 'quantum heat engines', 'high technology superconductors', 'quantum thermodynamics', 'magnetic semiconductors']</t>
+          <t>['high technology superconductors', 'quantum heat engines', 'ferroelectric materials', 'magnetic semiconductors', 'quantum thermodynamics']</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4912,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>['ecology', 'memory studies', 'art sustainability', 'visual culture', 'cinema', 'social movements culture', 'gender', 'sociology']</t>
+          <t>['social movements culture', 'gender', 'ecology', 'visual culture', 'art sustainability', 'memory studies', 'cinema', 'sociology']</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>['disadvantaged groups', 'family health', 'community health', 'violence', 'developmental needs']</t>
+          <t>['community health', 'disadvantaged groups', 'developmental needs', 'violence', 'family health']</t>
         </is>
       </c>
     </row>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>['nanotoxicity', 'nanomaterials', 'nanobiotechnology', 'raman spectroscopy']</t>
+          <t>['nanomaterials', 'nanotoxicity', 'raman spectroscopy', 'nanobiotechnology']</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>['climate change', 'fire safety building design', 'disaster management', 'naturebased solutions', 'urban water sensitivity', 'climate change resilient urban design', 'building materials building technologies architecture', 'postdisaster temporarypermanent housing studies']</t>
+          <t>['climate change resilient urban design', 'disaster management', 'fire safety building design', 'urban water sensitivity', 'naturebased solutions', 'climate change', 'building materials building technologies architecture', 'postdisaster temporarypermanent housing studies']</t>
         </is>
       </c>
     </row>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>['brand identity', 'olympic games', 'identification', 'sports marketing', 'life satisfaction', 'sponsorship', 'consumer behavior', 'social identity', 'event management', 'happiness']</t>
+          <t>['social identity', 'sponsorship', 'identification', 'event management', 'life satisfaction', 'consumer behavior', 'happiness', 'brand identity', 'sports marketing', 'olympic games']</t>
         </is>
       </c>
     </row>
@@ -4997,7 +4997,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>['computational fluid dynamics', 'parallel programming', 'computational heat transfer', 'modeling turbulent flows']</t>
+          <t>['parallel programming', 'computational heat transfer', 'modeling turbulent flows', 'computational fluid dynamics']</t>
         </is>
       </c>
     </row>
@@ -5014,7 +5014,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>['journalism', 'political communication', 'digital media', 'media studies']</t>
+          <t>['political communication', 'journalism', 'digital media', 'media studies']</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>['identity communication theories', 'smart cities', 'business model studies', 'gamification', 'cultural difference']</t>
+          <t>['business model studies', 'gamification', 'cultural difference', 'smart cities', 'identity communication theories']</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>['economic crises', 'international trade balance payments', 'gender economy', 'labor markets policies', 'macroeconomics', 'economic history', ' great depression']</t>
+          <t>['macroeconomics', 'gender economy', ' great depression', 'international trade balance payments', 'economic history', 'economic crises', 'labor markets policies']</t>
         </is>
       </c>
     </row>
@@ -5065,7 +5065,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>['social justice city', 'migration ethics', 'human rights theories', 'ethics datafication', 'ethics', 'commodification', 'smart cities']</t>
+          <t>['ethics datafication', 'commodification', 'social justice city', 'migration ethics', 'human rights theories', 'ethics', 'smart cities']</t>
         </is>
       </c>
     </row>
